--- a/5_figures/data/Validation target SH.xlsx
+++ b/5_figures/data/Validation target SH.xlsx
@@ -326,13 +326,13 @@
     <t xml:space="preserve">Pdgfr-alpha clone 3</t>
   </si>
   <si>
-    <t xml:space="preserve">Pdgfr-béta clone 7</t>
+    <t xml:space="preserve">Pdgfr-beta clone 7</t>
   </si>
   <si>
     <t xml:space="preserve">Pdgfrb</t>
   </si>
   <si>
-    <t xml:space="preserve">Pdgfr-béta clone 10</t>
+    <t xml:space="preserve">Pdgfr-beta clone 10</t>
   </si>
   <si>
     <t xml:space="preserve">MIF clone 1</t>
@@ -384,7 +384,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -414,12 +414,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -478,7 +472,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -527,10 +521,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1561,7 +1551,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B4:D62"/>
-  <sheetFormatPr defaultColWidth="10.5" defaultRowHeight="16" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.50390625" defaultRowHeight="16" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10.33"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16.33"/>
@@ -2522,7 +2512,7 @@
       <c r="A20" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="10" t="s">
         <v>90</v>
       </c>
       <c r="C20" s="10" t="s">
@@ -2545,7 +2535,7 @@
       <c r="A21" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="12" t="s">
+      <c r="B21" s="10" t="s">
         <v>90</v>
       </c>
       <c r="C21" s="10" t="s">
@@ -2568,7 +2558,7 @@
       <c r="A22" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="12" t="s">
+      <c r="B22" s="10" t="s">
         <v>90</v>
       </c>
       <c r="C22" s="10" t="s">
@@ -2591,7 +2581,7 @@
       <c r="A23" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="12" t="s">
+      <c r="B23" s="10" t="s">
         <v>90</v>
       </c>
       <c r="C23" s="10" t="s">
@@ -2614,7 +2604,7 @@
       <c r="A24" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="12" t="s">
+      <c r="B24" s="10" t="s">
         <v>90</v>
       </c>
       <c r="C24" s="10" t="s">
@@ -2637,7 +2627,7 @@
       <c r="A25" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B25" s="12" t="s">
+      <c r="B25" s="10" t="s">
         <v>90</v>
       </c>
       <c r="C25" s="10" t="s">
@@ -2660,7 +2650,7 @@
       <c r="A26" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="B26" s="12" t="s">
+      <c r="B26" s="10" t="s">
         <v>91</v>
       </c>
       <c r="C26" s="10" t="s">
@@ -2683,7 +2673,7 @@
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="12" t="s">
+      <c r="B27" s="10" t="s">
         <v>91</v>
       </c>
       <c r="C27" s="10" t="s">
@@ -2706,7 +2696,7 @@
       <c r="A28" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B28" s="12" t="s">
+      <c r="B28" s="10" t="s">
         <v>91</v>
       </c>
       <c r="C28" s="10" t="s">
@@ -2729,7 +2719,7 @@
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="B29" s="12" t="s">
+      <c r="B29" s="10" t="s">
         <v>91</v>
       </c>
       <c r="C29" s="10" t="s">
@@ -2752,7 +2742,7 @@
       <c r="A30" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="B30" s="12" t="s">
+      <c r="B30" s="10" t="s">
         <v>91</v>
       </c>
       <c r="C30" s="10" t="s">
@@ -2775,7 +2765,7 @@
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B31" s="12" t="s">
+      <c r="B31" s="10" t="s">
         <v>91</v>
       </c>
       <c r="C31" s="10" t="s">
@@ -2798,7 +2788,7 @@
       <c r="A32" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="B32" s="12" t="s">
+      <c r="B32" s="10" t="s">
         <v>93</v>
       </c>
       <c r="C32" s="10" t="s">
@@ -2821,7 +2811,7 @@
       <c r="A33" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B33" s="12" t="s">
+      <c r="B33" s="10" t="s">
         <v>93</v>
       </c>
       <c r="C33" s="10" t="s">
@@ -2844,7 +2834,7 @@
       <c r="A34" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="B34" s="12" t="s">
+      <c r="B34" s="10" t="s">
         <v>93</v>
       </c>
       <c r="C34" s="10" t="s">
@@ -2867,7 +2857,7 @@
       <c r="A35" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="B35" s="12" t="s">
+      <c r="B35" s="10" t="s">
         <v>93</v>
       </c>
       <c r="C35" s="10" t="s">
@@ -2890,7 +2880,7 @@
       <c r="A36" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B36" s="12" t="s">
+      <c r="B36" s="10" t="s">
         <v>93</v>
       </c>
       <c r="C36" s="10" t="s">
@@ -2913,7 +2903,7 @@
       <c r="A37" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="B37" s="12" t="s">
+      <c r="B37" s="10" t="s">
         <v>93</v>
       </c>
       <c r="C37" s="10" t="s">
@@ -2936,7 +2926,7 @@
       <c r="A38" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="B38" s="12" t="s">
+      <c r="B38" s="10" t="s">
         <v>94</v>
       </c>
       <c r="C38" s="10" t="s">
@@ -2959,7 +2949,7 @@
       <c r="A39" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B39" s="12" t="s">
+      <c r="B39" s="10" t="s">
         <v>94</v>
       </c>
       <c r="C39" s="10" t="s">
@@ -2982,7 +2972,7 @@
       <c r="A40" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="12" t="s">
+      <c r="B40" s="10" t="s">
         <v>94</v>
       </c>
       <c r="C40" s="10" t="s">
@@ -3005,7 +2995,7 @@
       <c r="A41" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="B41" s="12" t="s">
+      <c r="B41" s="10" t="s">
         <v>94</v>
       </c>
       <c r="C41" s="10" t="s">
@@ -3028,7 +3018,7 @@
       <c r="A42" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B42" s="12" t="s">
+      <c r="B42" s="10" t="s">
         <v>94</v>
       </c>
       <c r="C42" s="10" t="s">
@@ -3051,7 +3041,7 @@
       <c r="A43" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="B43" s="12" t="s">
+      <c r="B43" s="10" t="s">
         <v>94</v>
       </c>
       <c r="C43" s="10" t="s">
@@ -3074,7 +3064,7 @@
       <c r="A44" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B44" s="12" t="s">
+      <c r="B44" s="10" t="s">
         <v>96</v>
       </c>
       <c r="C44" s="10" t="s">
@@ -3097,7 +3087,7 @@
       <c r="A45" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B45" s="12" t="s">
+      <c r="B45" s="10" t="s">
         <v>96</v>
       </c>
       <c r="C45" s="10" t="s">
@@ -3120,7 +3110,7 @@
       <c r="A46" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B46" s="12" t="s">
+      <c r="B46" s="10" t="s">
         <v>96</v>
       </c>
       <c r="C46" s="10" t="s">
@@ -3143,7 +3133,7 @@
       <c r="A47" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B47" s="12" t="s">
+      <c r="B47" s="10" t="s">
         <v>96</v>
       </c>
       <c r="C47" s="10" t="s">
@@ -3166,7 +3156,7 @@
       <c r="A48" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B48" s="12" t="s">
+      <c r="B48" s="10" t="s">
         <v>96</v>
       </c>
       <c r="C48" s="10" t="s">
@@ -3189,7 +3179,7 @@
       <c r="A49" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="B49" s="12" t="s">
+      <c r="B49" s="10" t="s">
         <v>96</v>
       </c>
       <c r="C49" s="10" t="s">
@@ -3212,7 +3202,7 @@
       <c r="A50" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="B50" s="12" t="s">
+      <c r="B50" s="10" t="s">
         <v>97</v>
       </c>
       <c r="C50" s="10" t="s">
@@ -3235,7 +3225,7 @@
       <c r="A51" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="B51" s="12" t="s">
+      <c r="B51" s="10" t="s">
         <v>97</v>
       </c>
       <c r="C51" s="10" t="s">
@@ -3258,7 +3248,7 @@
       <c r="A52" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="B52" s="12" t="s">
+      <c r="B52" s="10" t="s">
         <v>97</v>
       </c>
       <c r="C52" s="10" t="s">
@@ -3281,7 +3271,7 @@
       <c r="A53" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B53" s="12" t="s">
+      <c r="B53" s="10" t="s">
         <v>97</v>
       </c>
       <c r="C53" s="10" t="s">
@@ -3304,7 +3294,7 @@
       <c r="A54" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="B54" s="12" t="s">
+      <c r="B54" s="10" t="s">
         <v>97</v>
       </c>
       <c r="C54" s="10" t="s">
@@ -3327,7 +3317,7 @@
       <c r="A55" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="B55" s="12" t="s">
+      <c r="B55" s="10" t="s">
         <v>97</v>
       </c>
       <c r="C55" s="10" t="s">
@@ -3350,7 +3340,7 @@
       <c r="A56" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="B56" s="12" t="s">
+      <c r="B56" s="10" t="s">
         <v>99</v>
       </c>
       <c r="C56" s="10" t="s">
@@ -3373,7 +3363,7 @@
       <c r="A57" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="B57" s="12" t="s">
+      <c r="B57" s="10" t="s">
         <v>99</v>
       </c>
       <c r="C57" s="10" t="s">
@@ -3396,7 +3386,7 @@
       <c r="A58" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="B58" s="12" t="s">
+      <c r="B58" s="10" t="s">
         <v>99</v>
       </c>
       <c r="C58" s="10" t="s">
@@ -3419,7 +3409,7 @@
       <c r="A59" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B59" s="12" t="s">
+      <c r="B59" s="10" t="s">
         <v>99</v>
       </c>
       <c r="C59" s="10" t="s">
@@ -3442,7 +3432,7 @@
       <c r="A60" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="B60" s="12" t="s">
+      <c r="B60" s="10" t="s">
         <v>99</v>
       </c>
       <c r="C60" s="10" t="s">
@@ -3465,7 +3455,7 @@
       <c r="A61" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="B61" s="12" t="s">
+      <c r="B61" s="10" t="s">
         <v>99</v>
       </c>
       <c r="C61" s="10" t="s">
@@ -3488,7 +3478,7 @@
       <c r="A62" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="B62" s="12" t="s">
+      <c r="B62" s="10" t="s">
         <v>100</v>
       </c>
       <c r="C62" s="10" t="s">
@@ -3511,7 +3501,7 @@
       <c r="A63" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="B63" s="12" t="s">
+      <c r="B63" s="10" t="s">
         <v>100</v>
       </c>
       <c r="C63" s="10" t="s">
@@ -3534,7 +3524,7 @@
       <c r="A64" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="B64" s="12" t="s">
+      <c r="B64" s="10" t="s">
         <v>100</v>
       </c>
       <c r="C64" s="10" t="s">
@@ -3557,7 +3547,7 @@
       <c r="A65" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="B65" s="12" t="s">
+      <c r="B65" s="10" t="s">
         <v>100</v>
       </c>
       <c r="C65" s="10" t="s">
@@ -3580,7 +3570,7 @@
       <c r="A66" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="B66" s="12" t="s">
+      <c r="B66" s="10" t="s">
         <v>100</v>
       </c>
       <c r="C66" s="10" t="s">
@@ -3603,7 +3593,7 @@
       <c r="A67" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B67" s="12" t="s">
+      <c r="B67" s="10" t="s">
         <v>100</v>
       </c>
       <c r="C67" s="10" t="s">
@@ -3626,7 +3616,7 @@
       <c r="A68" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="B68" s="12" t="s">
+      <c r="B68" s="10" t="s">
         <v>102</v>
       </c>
       <c r="C68" s="10" t="s">
@@ -3649,7 +3639,7 @@
       <c r="A69" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="B69" s="12" t="s">
+      <c r="B69" s="10" t="s">
         <v>102</v>
       </c>
       <c r="C69" s="10" t="s">
@@ -3672,7 +3662,7 @@
       <c r="A70" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="B70" s="12" t="s">
+      <c r="B70" s="10" t="s">
         <v>102</v>
       </c>
       <c r="C70" s="10" t="s">
@@ -3695,7 +3685,7 @@
       <c r="A71" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="B71" s="12" t="s">
+      <c r="B71" s="10" t="s">
         <v>102</v>
       </c>
       <c r="C71" s="10" t="s">
@@ -3718,7 +3708,7 @@
       <c r="A72" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="B72" s="12" t="s">
+      <c r="B72" s="10" t="s">
         <v>102</v>
       </c>
       <c r="C72" s="10" t="s">
@@ -3741,7 +3731,7 @@
       <c r="A73" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="B73" s="12" t="s">
+      <c r="B73" s="10" t="s">
         <v>102</v>
       </c>
       <c r="C73" s="10" t="s">
@@ -3764,7 +3754,7 @@
       <c r="A74" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="B74" s="12" t="s">
+      <c r="B74" s="10" t="s">
         <v>103</v>
       </c>
       <c r="C74" s="10" t="s">
@@ -3787,7 +3777,7 @@
       <c r="A75" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B75" s="12" t="s">
+      <c r="B75" s="10" t="s">
         <v>103</v>
       </c>
       <c r="C75" s="10" t="s">
@@ -3810,7 +3800,7 @@
       <c r="A76" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B76" s="12" t="s">
+      <c r="B76" s="10" t="s">
         <v>103</v>
       </c>
       <c r="C76" s="10" t="s">
@@ -3833,7 +3823,7 @@
       <c r="A77" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B77" s="12" t="s">
+      <c r="B77" s="10" t="s">
         <v>103</v>
       </c>
       <c r="C77" s="10" t="s">
@@ -3856,7 +3846,7 @@
       <c r="A78" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B78" s="12" t="s">
+      <c r="B78" s="10" t="s">
         <v>103</v>
       </c>
       <c r="C78" s="10" t="s">
@@ -3879,7 +3869,7 @@
       <c r="A79" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B79" s="12" t="s">
+      <c r="B79" s="10" t="s">
         <v>103</v>
       </c>
       <c r="C79" s="10" t="s">
@@ -3902,7 +3892,7 @@
       <c r="A80" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="B80" s="12" t="s">
+      <c r="B80" s="10" t="s">
         <v>105</v>
       </c>
       <c r="C80" s="10" t="s">
@@ -3925,7 +3915,7 @@
       <c r="A81" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B81" s="12" t="s">
+      <c r="B81" s="10" t="s">
         <v>105</v>
       </c>
       <c r="C81" s="10" t="s">
@@ -3948,7 +3938,7 @@
       <c r="A82" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B82" s="12" t="s">
+      <c r="B82" s="10" t="s">
         <v>105</v>
       </c>
       <c r="C82" s="10" t="s">
@@ -3971,7 +3961,7 @@
       <c r="A83" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B83" s="12" t="s">
+      <c r="B83" s="10" t="s">
         <v>105</v>
       </c>
       <c r="C83" s="10" t="s">
@@ -3994,7 +3984,7 @@
       <c r="A84" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B84" s="12" t="s">
+      <c r="B84" s="10" t="s">
         <v>105</v>
       </c>
       <c r="C84" s="10" t="s">
@@ -4017,7 +4007,7 @@
       <c r="A85" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B85" s="12" t="s">
+      <c r="B85" s="10" t="s">
         <v>105</v>
       </c>
       <c r="C85" s="10" t="s">
@@ -4040,7 +4030,7 @@
       <c r="A86" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="B86" s="12" t="s">
+      <c r="B86" s="10" t="s">
         <v>106</v>
       </c>
       <c r="C86" s="10" t="s">
@@ -4063,7 +4053,7 @@
       <c r="A87" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B87" s="12" t="s">
+      <c r="B87" s="10" t="s">
         <v>106</v>
       </c>
       <c r="C87" s="10" t="s">
@@ -4086,7 +4076,7 @@
       <c r="A88" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B88" s="12" t="s">
+      <c r="B88" s="10" t="s">
         <v>106</v>
       </c>
       <c r="C88" s="10" t="s">
@@ -4109,7 +4099,7 @@
       <c r="A89" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B89" s="12" t="s">
+      <c r="B89" s="10" t="s">
         <v>106</v>
       </c>
       <c r="C89" s="10" t="s">
@@ -4132,7 +4122,7 @@
       <c r="A90" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B90" s="12" t="s">
+      <c r="B90" s="10" t="s">
         <v>106</v>
       </c>
       <c r="C90" s="10" t="s">
@@ -4155,7 +4145,7 @@
       <c r="A91" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B91" s="12" t="s">
+      <c r="B91" s="10" t="s">
         <v>106</v>
       </c>
       <c r="C91" s="10" t="s">
@@ -4178,7 +4168,7 @@
       <c r="A92" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="B92" s="12" t="s">
+      <c r="B92" s="10" t="s">
         <v>107</v>
       </c>
       <c r="C92" s="10" t="s">
@@ -4201,7 +4191,7 @@
       <c r="A93" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B93" s="12" t="s">
+      <c r="B93" s="10" t="s">
         <v>107</v>
       </c>
       <c r="C93" s="10" t="s">
@@ -4224,7 +4214,7 @@
       <c r="A94" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B94" s="12" t="s">
+      <c r="B94" s="10" t="s">
         <v>107</v>
       </c>
       <c r="C94" s="10" t="s">
@@ -4247,7 +4237,7 @@
       <c r="A95" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B95" s="12" t="s">
+      <c r="B95" s="10" t="s">
         <v>107</v>
       </c>
       <c r="C95" s="10" t="s">
@@ -4270,7 +4260,7 @@
       <c r="A96" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B96" s="12" t="s">
+      <c r="B96" s="10" t="s">
         <v>107</v>
       </c>
       <c r="C96" s="10" t="s">
@@ -4293,7 +4283,7 @@
       <c r="A97" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B97" s="12" t="s">
+      <c r="B97" s="10" t="s">
         <v>107</v>
       </c>
       <c r="C97" s="10" t="s">
@@ -4316,7 +4306,7 @@
       <c r="A98" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="B98" s="12" t="s">
+      <c r="B98" s="10" t="s">
         <v>108</v>
       </c>
       <c r="C98" s="10" t="s">
@@ -4339,7 +4329,7 @@
       <c r="A99" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B99" s="12" t="s">
+      <c r="B99" s="10" t="s">
         <v>108</v>
       </c>
       <c r="C99" s="10" t="s">
@@ -4362,7 +4352,7 @@
       <c r="A100" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B100" s="12" t="s">
+      <c r="B100" s="10" t="s">
         <v>108</v>
       </c>
       <c r="C100" s="10" t="s">
@@ -4385,7 +4375,7 @@
       <c r="A101" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B101" s="12" t="s">
+      <c r="B101" s="10" t="s">
         <v>108</v>
       </c>
       <c r="C101" s="10" t="s">
@@ -4408,7 +4398,7 @@
       <c r="A102" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B102" s="12" t="s">
+      <c r="B102" s="10" t="s">
         <v>108</v>
       </c>
       <c r="C102" s="10" t="s">
@@ -4431,7 +4421,7 @@
       <c r="A103" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="B103" s="12" t="s">
+      <c r="B103" s="10" t="s">
         <v>110</v>
       </c>
       <c r="C103" s="10" t="s">
@@ -4454,7 +4444,7 @@
       <c r="A104" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B104" s="12" t="s">
+      <c r="B104" s="10" t="s">
         <v>110</v>
       </c>
       <c r="C104" s="10" t="s">
@@ -4477,7 +4467,7 @@
       <c r="A105" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B105" s="12" t="s">
+      <c r="B105" s="10" t="s">
         <v>110</v>
       </c>
       <c r="C105" s="10" t="s">
@@ -4500,7 +4490,7 @@
       <c r="A106" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B106" s="12" t="s">
+      <c r="B106" s="10" t="s">
         <v>110</v>
       </c>
       <c r="C106" s="10" t="s">
@@ -4523,7 +4513,7 @@
       <c r="A107" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B107" s="12" t="s">
+      <c r="B107" s="10" t="s">
         <v>110</v>
       </c>
       <c r="C107" s="10" t="s">
@@ -4546,7 +4536,7 @@
       <c r="A108" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B108" s="12" t="s">
+      <c r="B108" s="10" t="s">
         <v>110</v>
       </c>
       <c r="C108" s="10" t="s">
@@ -4624,8 +4614,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>